--- a/Data/27/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -220,7 +220,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699424</t>
+    <t>10699522</t>
   </si>
   <si>
     <t>Passed</t>
@@ -235,10 +235,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Clay</t>
-  </si>
-  <si>
-    <t>Kuhic</t>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Wyman</t>
   </si>
   <si>
     <t>067898707</t>
@@ -359,19 +359,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699425</t>
+    <t>10699523</t>
   </si>
   <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
   </si>
   <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Quigley</t>
-  </si>
-  <si>
-    <t>Auto 56030197</t>
+    <t>Jayme</t>
+  </si>
+  <si>
+    <t>Runolfsdottir</t>
+  </si>
+  <si>
+    <t>Auto 9304849</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L2" s="16">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45774</v>
+        <v>45779</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>71</v>
@@ -1275,11 +1275,11 @@
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45774</v>
+        <v>45779</v>
       </c>
       <c r="Y2" s="16">
         <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
-        <v>45825</v>
+        <v>45830</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>85</v>
@@ -1343,11 +1343,11 @@
       </c>
       <c r="AT2" s="18">
         <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
-        <v>45773</v>
+        <v>45778</v>
       </c>
       <c r="AU2" s="18">
         <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
-        <v>45773</v>
+        <v>45778</v>
       </c>
       <c r="AV2" s="29">
         <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="BD2" s="32" t="str">
         <f>BH9</f>
-        <v>MTKBNN10D10A356A</v>
+        <v>MTKBNN10D10A170A</v>
       </c>
       <c r="BE2" t="s">
         <v>103</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L3" s="16">
         <f t="shared" si="0"/>
-        <v>45774</v>
+        <v>45779</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>71</v>
@@ -1495,11 +1495,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" si="1"/>
-        <v>45774</v>
+        <v>45779</v>
       </c>
       <c r="Y3" s="16">
         <f t="shared" si="2"/>
-        <v>45825</v>
+        <v>45830</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>85</v>
@@ -1563,11 +1563,11 @@
       </c>
       <c r="AT3" s="18">
         <f t="shared" si="3"/>
-        <v>45773</v>
+        <v>45778</v>
       </c>
       <c r="AU3" s="18">
         <f t="shared" si="4"/>
-        <v>45773</v>
+        <v>45778</v>
       </c>
       <c r="AV3" s="29">
         <f t="shared" si="5"/>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="BD3" s="32" t="str">
         <f>BH10</f>
-        <v>MTKNBN20D20A696A</v>
+        <v>MTKNBN20D20A891A</v>
       </c>
       <c r="BE3" t="s">
         <v>103</v>
@@ -1666,28 +1666,28 @@
       </c>
       <c r="AX9">
         <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>72848</v>
+        <v>25785</v>
       </c>
       <c r="AY9" t="s">
         <v>125</v>
       </c>
       <c r="AZ9" t="str">
         <f>AW9&amp;AX9&amp;AY9</f>
-        <v>AB72848JC</v>
+        <v>AB25785JC</v>
       </c>
       <c r="BD9" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE9">
         <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>356</v>
+        <v>170</v>
       </c>
       <c r="BG9" t="s">
         <v>127</v>
       </c>
       <c r="BH9" t="str">
         <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A356A</v>
+        <v>MTKBNN10D10A170A</v>
       </c>
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1696,27 +1696,27 @@
         <v>128</v>
       </c>
       <c r="AX10">
-        <v>19176</v>
+        <v>24890</v>
       </c>
       <c r="AY10" t="s">
         <v>129</v>
       </c>
       <c r="AZ10" t="str">
         <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA19176CJ</v>
+        <v>BA24890CJ</v>
       </c>
       <c r="BD10" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE10">
-        <v>696</v>
+        <v>891</v>
       </c>
       <c r="BG10" t="s">
         <v>127</v>
       </c>
       <c r="BH10" t="str">
         <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A696A</v>
+        <v>MTKNBN20D20A891A</v>
       </c>
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1725,27 +1725,27 @@
         <v>124</v>
       </c>
       <c r="AX11">
-        <v>72651</v>
+        <v>71290</v>
       </c>
       <c r="AY11" t="s">
         <v>125</v>
       </c>
       <c r="AZ11" t="str">
         <f t="shared" si="6"/>
-        <v>AB72651JC</v>
+        <v>AB71290JC</v>
       </c>
       <c r="BD11" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE11">
-        <v>434</v>
+        <v>531</v>
       </c>
       <c r="BG11" t="s">
         <v>127</v>
       </c>
       <c r="BH11" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A434A</v>
+        <v>MTKBNN10D10A531A</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1754,27 +1754,27 @@
         <v>128</v>
       </c>
       <c r="AX12">
-        <v>18652</v>
+        <v>42997</v>
       </c>
       <c r="AY12" t="s">
         <v>129</v>
       </c>
       <c r="AZ12" t="str">
         <f t="shared" si="6"/>
-        <v>BA18652CJ</v>
+        <v>BA42997CJ</v>
       </c>
       <c r="BD12" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE12">
-        <v>568</v>
+        <v>256</v>
       </c>
       <c r="BG12" t="s">
         <v>127</v>
       </c>
       <c r="BH12" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A568A</v>
+        <v>MTKNBN20D20A256A</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1783,27 +1783,27 @@
         <v>124</v>
       </c>
       <c r="AX13">
-        <v>78664</v>
+        <v>40177</v>
       </c>
       <c r="AY13" t="s">
         <v>125</v>
       </c>
       <c r="AZ13" t="str">
         <f t="shared" si="6"/>
-        <v>AB78664JC</v>
+        <v>AB40177JC</v>
       </c>
       <c r="BD13" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE13">
-        <v>311</v>
+        <v>525</v>
       </c>
       <c r="BG13" t="s">
         <v>127</v>
       </c>
       <c r="BH13" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A311A</v>
+        <v>MTKBNN10D10A525A</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1812,27 +1812,27 @@
         <v>128</v>
       </c>
       <c r="AX14">
-        <v>15730</v>
+        <v>16837</v>
       </c>
       <c r="AY14" t="s">
         <v>129</v>
       </c>
       <c r="AZ14" t="str">
         <f t="shared" si="6"/>
-        <v>BA15730CJ</v>
+        <v>BA16837CJ</v>
       </c>
       <c r="BD14" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE14">
-        <v>904</v>
+        <v>562</v>
       </c>
       <c r="BG14" t="s">
         <v>127</v>
       </c>
       <c r="BH14" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A904A</v>
+        <v>MTKNBN20D20A562A</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1841,27 +1841,27 @@
         <v>124</v>
       </c>
       <c r="AX15">
-        <v>67702</v>
+        <v>24723</v>
       </c>
       <c r="AY15" t="s">
         <v>125</v>
       </c>
       <c r="AZ15" t="str">
         <f t="shared" si="6"/>
-        <v>AB67702JC</v>
+        <v>AB24723JC</v>
       </c>
       <c r="BD15" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE15">
-        <v>794</v>
+        <v>927</v>
       </c>
       <c r="BG15" t="s">
         <v>127</v>
       </c>
       <c r="BH15" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A794A</v>
+        <v>MTKBNN10D10A927A</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1870,27 +1870,27 @@
         <v>128</v>
       </c>
       <c r="AX16">
-        <v>44128</v>
+        <v>62926</v>
       </c>
       <c r="AY16" t="s">
         <v>129</v>
       </c>
       <c r="AZ16" t="str">
         <f t="shared" si="6"/>
-        <v>BA44128CJ</v>
+        <v>BA62926CJ</v>
       </c>
       <c r="BD16" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE16">
-        <v>525</v>
+        <v>876</v>
       </c>
       <c r="BG16" t="s">
         <v>127</v>
       </c>
       <c r="BH16" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A525A</v>
+        <v>MTKNBN20D20A876A</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1899,27 +1899,27 @@
         <v>124</v>
       </c>
       <c r="AX17">
-        <v>65002</v>
+        <v>59916</v>
       </c>
       <c r="AY17" t="s">
         <v>125</v>
       </c>
       <c r="AZ17" t="str">
         <f t="shared" si="6"/>
-        <v>AB65002JC</v>
+        <v>AB59916JC</v>
       </c>
       <c r="BD17" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE17">
-        <v>934</v>
+        <v>235</v>
       </c>
       <c r="BG17" t="s">
         <v>127</v>
       </c>
       <c r="BH17" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A934A</v>
+        <v>MTKBNN10D10A235A</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1928,27 +1928,27 @@
         <v>128</v>
       </c>
       <c r="AX18">
-        <v>74796</v>
+        <v>98951</v>
       </c>
       <c r="AY18" t="s">
         <v>129</v>
       </c>
       <c r="AZ18" t="str">
         <f t="shared" si="6"/>
-        <v>BA74796CJ</v>
+        <v>BA98951CJ</v>
       </c>
       <c r="BD18" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE18">
-        <v>833</v>
+        <v>363</v>
       </c>
       <c r="BG18" t="s">
         <v>127</v>
       </c>
       <c r="BH18" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A833A</v>
+        <v>MTKNBN20D20A363A</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1956,27 +1956,27 @@
         <v>124</v>
       </c>
       <c r="AX19">
-        <v>88461</v>
+        <v>62936</v>
       </c>
       <c r="AY19" t="s">
         <v>125</v>
       </c>
       <c r="AZ19" t="str">
         <f t="shared" si="6"/>
-        <v>AB88461JC</v>
+        <v>AB62936JC</v>
       </c>
       <c r="BD19" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE19">
-        <v>778</v>
+        <v>274</v>
       </c>
       <c r="BG19" t="s">
         <v>127</v>
       </c>
       <c r="BH19" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A778A</v>
+        <v>MTKBNN10D10A274A</v>
       </c>
     </row>
     <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1984,27 +1984,27 @@
         <v>128</v>
       </c>
       <c r="AX20">
-        <v>56636</v>
+        <v>22349</v>
       </c>
       <c r="AY20" t="s">
         <v>129</v>
       </c>
       <c r="AZ20" t="str">
         <f t="shared" si="6"/>
-        <v>BA56636CJ</v>
+        <v>BA22349CJ</v>
       </c>
       <c r="BD20" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE20">
-        <v>448</v>
+        <v>892</v>
       </c>
       <c r="BG20" t="s">
         <v>127</v>
       </c>
       <c r="BH20" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A448A</v>
+        <v>MTKNBN20D20A892A</v>
       </c>
     </row>
     <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2012,27 +2012,27 @@
         <v>124</v>
       </c>
       <c r="AX21">
-        <v>59776</v>
+        <v>90020</v>
       </c>
       <c r="AY21" t="s">
         <v>125</v>
       </c>
       <c r="AZ21" t="str">
         <f t="shared" si="6"/>
-        <v>AB59776JC</v>
+        <v>AB90020JC</v>
       </c>
       <c r="BD21" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE21">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="BG21" t="s">
         <v>127</v>
       </c>
       <c r="BH21" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A278A</v>
+        <v>MTKBNN10D10A251A</v>
       </c>
     </row>
     <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2040,27 +2040,27 @@
         <v>128</v>
       </c>
       <c r="AX22">
-        <v>88250</v>
+        <v>93643</v>
       </c>
       <c r="AY22" t="s">
         <v>129</v>
       </c>
       <c r="AZ22" t="str">
         <f t="shared" si="6"/>
-        <v>BA88250CJ</v>
+        <v>BA93643CJ</v>
       </c>
       <c r="BD22" s="32" t="s">
         <v>130</v>
       </c>
       <c r="BE22">
-        <v>577</v>
+        <v>992</v>
       </c>
       <c r="BG22" t="s">
         <v>127</v>
       </c>
       <c r="BH22" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A577A</v>
+        <v>MTKNBN20D20A992A</v>
       </c>
     </row>
     <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2068,27 +2068,27 @@
         <v>124</v>
       </c>
       <c r="AX23">
-        <v>24154</v>
+        <v>79028</v>
       </c>
       <c r="AY23" t="s">
         <v>125</v>
       </c>
       <c r="AZ23" t="str">
         <f t="shared" si="6"/>
-        <v>AB24154JC</v>
+        <v>AB79028JC</v>
       </c>
       <c r="BD23" s="32" t="s">
         <v>126</v>
       </c>
       <c r="BE23">
-        <v>363</v>
+        <v>155</v>
       </c>
       <c r="BG23" t="s">
         <v>127</v>
       </c>
       <c r="BH23" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A363A</v>
+        <v>MTKBNN10D10A155A</v>
       </c>
     </row>
   </sheetData>

--- a/Data/27/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{67946AE5-3CCA-43BF-98A4-DFC5BD5B3717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="128">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -218,12 +233,6 @@
   </si>
   <si>
     <t>Test_1</t>
-  </si>
-  <si>
-    <t>10699522</t>
-  </si>
-  <si>
-    <t>Passed</t>
   </si>
   <si>
     <t>275 Recruitment (Zojez Vizyzi (10279378))</t>
@@ -357,9 +366,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699523</t>
   </si>
   <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
@@ -413,59 +419,59 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4A4A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF4A4A4A"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -477,13 +483,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,22 +526,40 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -928,9 +952,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BR23"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="65.90625" customWidth="1"/>
@@ -990,7 +1014,7 @@
     <col min="70" max="70" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:70" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1202,99 +1226,95 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="I2" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="L2" s="16">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45786</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="O2" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="L2" s="16">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="P2" s="17">
         <v>1</v>
       </c>
       <c r="Q2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T2" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="U2" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" s="18" t="s">
+      <c r="V2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="W2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="X2" s="20">
+        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
+        <v>45786</v>
+      </c>
+      <c r="Y2" s="16">
+        <f t="shared" ref="Y2:Y3" ca="1" si="2">TODAY()+20</f>
+        <v>45837</v>
+      </c>
+      <c r="Z2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="V2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W2" s="15" t="s">
+      <c r="AA2" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="20">
-        <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45779</v>
-      </c>
-      <c r="Y2" s="16">
-        <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
-        <v>45830</v>
-      </c>
-      <c r="Z2" s="15" t="s">
+      <c r="AB2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AC2" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="AB2" s="22" t="s">
+      <c r="AD2" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="AC2" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD2" s="22" t="s">
-        <v>89</v>
       </c>
       <c r="AE2" s="11">
         <v>275</v>
@@ -1306,215 +1326,211 @@
         <v>40</v>
       </c>
       <c r="AH2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ2" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AJ2" s="26" t="s">
+      <c r="AL2" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AM2" t="s">
         <v>93</v>
       </c>
-      <c r="AL2" s="15" t="s">
+      <c r="AN2" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AO2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AN2" s="15" t="s">
+      <c r="AP2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AQ2" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AR2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS2" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="AQ2" s="27" t="s">
+      <c r="AT2" s="18">
+        <f t="shared" ref="AT2:AT3" ca="1" si="3">X2-1</f>
+        <v>45785</v>
+      </c>
+      <c r="AU2" s="18">
+        <f t="shared" ref="AU2:AU3" ca="1" si="4">X2-1</f>
+        <v>45785</v>
+      </c>
+      <c r="AV2" s="29" t="str">
+        <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AW2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AZ2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AR2" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="AS2" s="28" t="s">
+      <c r="BA2" s="31" t="str">
+        <f ca="1">AZ9</f>
+        <v>AB76001JC</v>
+      </c>
+      <c r="BB2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AT2" s="18">
-        <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
-        <v>45778</v>
-      </c>
-      <c r="AU2" s="18">
-        <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
-        <v>45778</v>
-      </c>
-      <c r="AV2" s="29">
-        <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AW2" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AZ2" s="31" t="s">
+      <c r="BD2" s="32" t="str">
+        <f ca="1">BH9</f>
+        <v>MTKBNN10D10A322A</v>
+      </c>
+      <c r="BE2" t="s">
         <v>101</v>
-      </c>
-      <c r="BA2" s="31">
-        <f>AZ9</f>
-        <v>NaN</v>
-      </c>
-      <c r="BB2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BC2" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD2" s="32" t="str">
-        <f>BH9</f>
-        <v>MTKBNN10D10A170A</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>103</v>
       </c>
       <c r="BF2" s="33">
         <v>35591</v>
       </c>
       <c r="BG2" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BH2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BI2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK2" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" s="11" t="s">
+      <c r="BL2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" s="33" t="s">
+      <c r="BN2" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BM2" s="11" t="s">
+      <c r="BO2" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="BN2" s="31" t="s">
+      <c r="BP2" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="BO2" s="31" t="s">
+      <c r="BQ2" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="BP2" s="31" t="s">
+      <c r="BR2" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BQ2" s="31" t="s">
+    </row>
+    <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>111</v>
       </c>
-      <c r="BR2" s="15" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="10" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="H3" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" s="16">
+        <f t="shared" ca="1" si="0"/>
+        <v>45786</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" s="15" t="s">
+      <c r="N3" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="O3" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="L3" s="16">
-        <f t="shared" si="0"/>
-        <v>45779</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="P3" s="17">
         <v>1</v>
       </c>
       <c r="Q3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="U3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T3" s="18" t="s">
+      <c r="V3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="U3" s="19" t="s">
+      <c r="X3" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>45786</v>
+      </c>
+      <c r="Y3" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45837</v>
+      </c>
+      <c r="Z3" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="V3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="X3" s="20">
-        <f t="shared" si="1"/>
-        <v>45779</v>
-      </c>
-      <c r="Y3" s="16">
-        <f t="shared" si="2"/>
-        <v>45830</v>
-      </c>
-      <c r="Z3" s="15" t="s">
+      <c r="AA3" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB3" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AA3" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB3" s="22" t="s">
+      <c r="AC3" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD3" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="AC3" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" s="22" t="s">
-        <v>89</v>
       </c>
       <c r="AE3" s="11">
         <v>275</v>
@@ -1526,600 +1542,613 @@
         <v>40</v>
       </c>
       <c r="AH3" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ3" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AK3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AJ3" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK3" s="15" t="s">
-        <v>93</v>
-      </c>
       <c r="AL3" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="AM3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AN3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="AQ3" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS3" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT3" s="18">
+        <f t="shared" ca="1" si="3"/>
+        <v>45785</v>
+      </c>
+      <c r="AU3" s="18">
+        <f t="shared" ca="1" si="4"/>
+        <v>45785</v>
+      </c>
+      <c r="AV3" s="29" t="str">
+        <f t="shared" si="5"/>
+        <v>N/A</v>
+      </c>
+      <c r="AW3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX3" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AZ3" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AR3" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="AS3" s="28" t="s">
+      <c r="BA3" s="31" t="str">
+        <f ca="1">AZ10</f>
+        <v>BA35334CJ</v>
+      </c>
+      <c r="BB3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC3" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AT3" s="18">
-        <f t="shared" si="3"/>
-        <v>45778</v>
-      </c>
-      <c r="AU3" s="18">
-        <f t="shared" si="4"/>
-        <v>45778</v>
-      </c>
-      <c r="AV3" s="29">
-        <f t="shared" si="5"/>
-        <v>NaN</v>
-      </c>
-      <c r="AW3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AZ3" s="31" t="s">
+      <c r="BD3" s="32" t="str">
+        <f ca="1">BH10</f>
+        <v>MTKNBN20D20A694A</v>
+      </c>
+      <c r="BE3" t="s">
         <v>101</v>
-      </c>
-      <c r="BA3" s="31">
-        <f>AZ10</f>
-        <v>NaN</v>
-      </c>
-      <c r="BB3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BC3" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD3" s="32" t="str">
-        <f>BH10</f>
-        <v>MTKNBN20D20A891A</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>103</v>
       </c>
       <c r="BF3" s="33">
         <v>35591</v>
       </c>
       <c r="BG3" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BH3" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BI3" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BJ3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK3" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ3" s="11" t="s">
+      <c r="BL3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM3" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BK3" s="33" t="s">
+      <c r="BN3" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="BL3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BM3" s="11" t="s">
+      <c r="BO3" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="BN3" s="31" t="s">
+      <c r="BP3" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="BO3" s="31" t="s">
+      <c r="BQ3" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="BP3" s="31" t="s">
+      <c r="BR3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BQ3" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="BR3" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="3:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C4" s="9"/>
       <c r="AZ4" s="7"/>
       <c r="BA4" s="34"/>
     </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C8" s="9"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="9"/>
       <c r="AW9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX9">
+        <f t="array" aca="1" ref="AX9:AX23" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
+        <v>76001</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ9" t="str">
+        <f ca="1">AW9&amp;AX9&amp;AY9</f>
+        <v>AB76001JC</v>
+      </c>
+      <c r="BD9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE9">
+        <f t="array" aca="1" ref="BE9:BE23" ca="1">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
+        <v>322</v>
+      </c>
+      <c r="BG9" t="s">
         <v>124</v>
       </c>
-      <c r="AX9">
-        <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>25785</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ9" t="str">
-        <f>AW9&amp;AX9&amp;AY9</f>
-        <v>AB25785JC</v>
-      </c>
-      <c r="BD9" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE9">
-        <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>170</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>127</v>
-      </c>
       <c r="BH9" t="str">
-        <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A170A</v>
-      </c>
-    </row>
-    <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f ca="1">BD9&amp;BE9&amp;BF9&amp;BG9</f>
+        <v>MTKBNN10D10A322A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="9"/>
       <c r="AW10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX10">
-        <v>24890</v>
+        <f ca="1"/>
+        <v>35334</v>
       </c>
       <c r="AY10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ10" t="str">
-        <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA24890CJ</v>
+        <f t="shared" ref="AZ10:AZ23" ca="1" si="6">AW10&amp;AX10&amp;AY10</f>
+        <v>BA35334CJ</v>
       </c>
       <c r="BD10" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE10">
-        <v>891</v>
+        <f ca="1"/>
+        <v>694</v>
       </c>
       <c r="BG10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH10" t="str">
-        <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A891A</v>
-      </c>
-    </row>
-    <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BH10:BH23" ca="1" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
+        <v>MTKNBN20D20A694A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="9"/>
       <c r="AW11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX11">
+        <f ca="1"/>
+        <v>75717</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ11" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB75717JC</v>
+      </c>
+      <c r="BD11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE11">
+        <f ca="1"/>
+        <v>962</v>
+      </c>
+      <c r="BG11" t="s">
         <v>124</v>
       </c>
-      <c r="AX11">
-        <v>71290</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ11" t="str">
-        <f t="shared" si="6"/>
-        <v>AB71290JC</v>
-      </c>
-      <c r="BD11" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE11">
-        <v>531</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>127</v>
-      </c>
       <c r="BH11" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A531A</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A962A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="9"/>
       <c r="AW12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX12">
-        <v>42997</v>
+        <f ca="1"/>
+        <v>35938</v>
       </c>
       <c r="AY12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ12" t="str">
-        <f t="shared" si="6"/>
-        <v>BA42997CJ</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA35938CJ</v>
       </c>
       <c r="BD12" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE12">
-        <v>256</v>
+        <f ca="1"/>
+        <v>949</v>
       </c>
       <c r="BG12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH12" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A256A</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A949A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="9"/>
       <c r="AW13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX13">
+        <f ca="1"/>
+        <v>16553</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ13" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB16553JC</v>
+      </c>
+      <c r="BD13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE13">
+        <f ca="1"/>
+        <v>476</v>
+      </c>
+      <c r="BG13" t="s">
         <v>124</v>
       </c>
-      <c r="AX13">
-        <v>40177</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ13" t="str">
-        <f t="shared" si="6"/>
-        <v>AB40177JC</v>
-      </c>
-      <c r="BD13" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE13">
-        <v>525</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>127</v>
-      </c>
       <c r="BH13" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A525A</v>
-      </c>
-    </row>
-    <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A476A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="9"/>
       <c r="AW14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX14">
-        <v>16837</v>
+        <f ca="1"/>
+        <v>48038</v>
       </c>
       <c r="AY14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ14" t="str">
-        <f t="shared" si="6"/>
-        <v>BA16837CJ</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA48038CJ</v>
       </c>
       <c r="BD14" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE14">
-        <v>562</v>
+        <f ca="1"/>
+        <v>382</v>
       </c>
       <c r="BG14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH14" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A562A</v>
-      </c>
-    </row>
-    <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A382A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="9"/>
       <c r="AW15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX15">
+        <f ca="1"/>
+        <v>93019</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ15" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB93019JC</v>
+      </c>
+      <c r="BD15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE15">
+        <f ca="1"/>
+        <v>907</v>
+      </c>
+      <c r="BG15" t="s">
         <v>124</v>
       </c>
-      <c r="AX15">
-        <v>24723</v>
-      </c>
-      <c r="AY15" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ15" t="str">
-        <f t="shared" si="6"/>
-        <v>AB24723JC</v>
-      </c>
-      <c r="BD15" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE15">
-        <v>927</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>127</v>
-      </c>
       <c r="BH15" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A927A</v>
-      </c>
-    </row>
-    <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A907A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="9"/>
       <c r="AW16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX16">
-        <v>62926</v>
+        <f ca="1"/>
+        <v>12745</v>
       </c>
       <c r="AY16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AZ16" t="str">
-        <f t="shared" si="6"/>
-        <v>BA62926CJ</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>BA12745CJ</v>
       </c>
       <c r="BD16" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BE16">
-        <v>876</v>
+        <f ca="1"/>
+        <v>784</v>
       </c>
       <c r="BG16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="BH16" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A876A</v>
-      </c>
-    </row>
-    <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A784A</v>
+      </c>
+    </row>
+    <row r="17" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
       <c r="AW17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX17">
+        <f ca="1"/>
+        <v>47691</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ17" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB47691JC</v>
+      </c>
+      <c r="BD17" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE17">
+        <f ca="1"/>
+        <v>487</v>
+      </c>
+      <c r="BG17" t="s">
         <v>124</v>
       </c>
-      <c r="AX17">
-        <v>59916</v>
-      </c>
-      <c r="AY17" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ17" t="str">
-        <f t="shared" si="6"/>
-        <v>AB59916JC</v>
-      </c>
-      <c r="BD17" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE17">
-        <v>235</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>127</v>
-      </c>
       <c r="BH17" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A235A</v>
-      </c>
-    </row>
-    <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A487A</v>
+      </c>
+    </row>
+    <row r="18" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="AW18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AX18">
-        <v>98951</v>
+        <f ca="1"/>
+        <v>70762</v>
       </c>
       <c r="AY18" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ18" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>BA70762CJ</v>
+      </c>
+      <c r="BD18" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE18">
+        <f ca="1"/>
+        <v>890</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH18" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A890A</v>
+      </c>
+    </row>
+    <row r="19" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AW19" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX19">
+        <f ca="1"/>
+        <v>63720</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ19" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB63720JC</v>
+      </c>
+      <c r="BD19" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE19">
+        <f ca="1"/>
         <v>129</v>
       </c>
-      <c r="AZ18" t="str">
-        <f t="shared" si="6"/>
-        <v>BA98951CJ</v>
-      </c>
-      <c r="BD18" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE18">
-        <v>363</v>
-      </c>
-      <c r="BG18" t="s">
+      <c r="BG19" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH19" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A129A</v>
+      </c>
+    </row>
+    <row r="20" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AW20" t="s">
+        <v>125</v>
+      </c>
+      <c r="AX20">
+        <f ca="1"/>
+        <v>43549</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ20" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>BA43549CJ</v>
+      </c>
+      <c r="BD20" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BH18" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A363A</v>
-      </c>
-    </row>
-    <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW19" t="s">
+      <c r="BE20">
+        <f ca="1"/>
+        <v>676</v>
+      </c>
+      <c r="BG20" t="s">
         <v>124</v>
       </c>
-      <c r="AX19">
-        <v>62936</v>
-      </c>
-      <c r="AY19" t="s">
+      <c r="BH20" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A676A</v>
+      </c>
+    </row>
+    <row r="21" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AW21" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX21">
+        <f ca="1"/>
+        <v>18605</v>
+      </c>
+      <c r="AY21" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ21" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB18605JC</v>
+      </c>
+      <c r="BD21" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE21">
+        <f ca="1"/>
+        <v>201</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH21" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A201A</v>
+      </c>
+    </row>
+    <row r="22" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AW22" t="s">
         <v>125</v>
       </c>
-      <c r="AZ19" t="str">
-        <f t="shared" si="6"/>
-        <v>AB62936JC</v>
-      </c>
-      <c r="BD19" s="32" t="s">
+      <c r="AX22">
+        <f ca="1"/>
+        <v>65277</v>
+      </c>
+      <c r="AY22" t="s">
         <v>126</v>
       </c>
-      <c r="BE19">
-        <v>274</v>
-      </c>
-      <c r="BG19" t="s">
+      <c r="AZ22" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>BA65277CJ</v>
+      </c>
+      <c r="BD22" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BH19" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A274A</v>
-      </c>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW20" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX20">
-        <v>22349</v>
-      </c>
-      <c r="AY20" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ20" t="str">
-        <f t="shared" si="6"/>
-        <v>BA22349CJ</v>
-      </c>
-      <c r="BD20" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE20">
-        <v>892</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>127</v>
-      </c>
-      <c r="BH20" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A892A</v>
-      </c>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW21" t="s">
+      <c r="BE22">
+        <f ca="1"/>
+        <v>730</v>
+      </c>
+      <c r="BG22" t="s">
         <v>124</v>
       </c>
-      <c r="AX21">
-        <v>90020</v>
-      </c>
-      <c r="AY21" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ21" t="str">
-        <f t="shared" si="6"/>
-        <v>AB90020JC</v>
-      </c>
-      <c r="BD21" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE21">
-        <v>251</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>127</v>
-      </c>
-      <c r="BH21" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A251A</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
-      <c r="AW22" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX22">
-        <v>93643</v>
-      </c>
-      <c r="AY22" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ22" t="str">
-        <f t="shared" si="6"/>
-        <v>BA93643CJ</v>
-      </c>
-      <c r="BD22" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE22">
-        <v>992</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>127</v>
-      </c>
       <c r="BH22" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKNBN20D20A992A</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKNBN20D20A730A</v>
+      </c>
+    </row>
+    <row r="23" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AW23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX23">
+        <f ca="1"/>
+        <v>60009</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ23" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>AB60009JC</v>
+      </c>
+      <c r="BD23" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE23">
+        <f ca="1"/>
+        <v>850</v>
+      </c>
+      <c r="BG23" t="s">
         <v>124</v>
       </c>
-      <c r="AX23">
-        <v>79028</v>
-      </c>
-      <c r="AY23" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ23" t="str">
-        <f t="shared" si="6"/>
-        <v>AB79028JC</v>
-      </c>
-      <c r="BD23" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE23">
-        <v>155</v>
-      </c>
-      <c r="BG23" t="s">
-        <v>127</v>
-      </c>
       <c r="BH23" t="str">
-        <f t="shared" si="7"/>
-        <v>MTKBNN10D10A155A</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>MTKBNN10D10A850A</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ2:BQ3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS3 Z2:Z3 V2:V3 S2:S3 K2:K3 BQ2:BQ3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1"/>
-    <hyperlink ref="U2" r:id="rId2"/>
-    <hyperlink ref="AH2" r:id="rId3"/>
-    <hyperlink ref="I3" r:id="rId4"/>
-    <hyperlink ref="U3" r:id="rId5"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="AH2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="U3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/27/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{67946AE5-3CCA-43BF-98A4-DFC5BD5B3717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{F706DC4D-A627-4F02-8DE5-7222689E8301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="129">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -244,10 +244,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Benjamin</t>
-  </si>
-  <si>
-    <t>Wyman</t>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>Kling</t>
   </si>
   <si>
     <t>067898707</t>
@@ -371,13 +371,13 @@
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
   </si>
   <si>
-    <t>Jayme</t>
-  </si>
-  <si>
-    <t>Runolfsdottir</t>
-  </si>
-  <si>
-    <t>Auto 9304849</t>
+    <t>Sydni</t>
+  </si>
+  <si>
+    <t>Heller</t>
+  </si>
+  <si>
+    <t>Auto 90898336</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t>MTKNBN20D20A</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
 </sst>
 </file>
@@ -501,7 +504,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -577,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -662,6 +665,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1226,12 +1233,16 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="8">
+        <v>10699758</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="D2" s="10" t="s">
         <v>68</v>
       </c>
@@ -1258,7 +1269,7 @@
       </c>
       <c r="L2" s="16">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>69</v>
@@ -1295,11 +1306,11 @@
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="Y2" s="16">
         <f t="shared" ref="Y2:Y3" ca="1" si="2">TODAY()+20</f>
-        <v>45837</v>
+        <v>45847</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>83</v>
@@ -1363,11 +1374,11 @@
       </c>
       <c r="AT2" s="18">
         <f t="shared" ref="AT2:AT3" ca="1" si="3">X2-1</f>
-        <v>45785</v>
+        <v>45795</v>
       </c>
       <c r="AU2" s="18">
         <f t="shared" ref="AU2:AU3" ca="1" si="4">X2-1</f>
-        <v>45785</v>
+        <v>45795</v>
       </c>
       <c r="AV2" s="29" t="str">
         <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
@@ -1385,9 +1396,9 @@
       <c r="AZ2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="BA2" s="31" t="str">
+      <c r="BA2" s="32" t="str">
         <f ca="1">AZ9</f>
-        <v>AB76001JC</v>
+        <v>AB73464JC</v>
       </c>
       <c r="BB2" s="11" t="s">
         <v>69</v>
@@ -1395,14 +1406,14 @@
       <c r="BC2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="BD2" s="32" t="str">
+      <c r="BD2" s="33" t="str">
         <f ca="1">BH9</f>
-        <v>MTKBNN10D10A322A</v>
+        <v>MTKBNN10D10A236A</v>
       </c>
       <c r="BE2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" s="33">
+      <c r="BF2" s="34">
         <v>35591</v>
       </c>
       <c r="BG2" s="11" t="s">
@@ -1417,7 +1428,7 @@
       <c r="BJ2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BK2" s="33" t="s">
+      <c r="BK2" s="34" t="s">
         <v>104</v>
       </c>
       <c r="BL2" s="11" t="s">
@@ -1442,12 +1453,16 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
+      <c r="B3" s="8">
+        <v>10699742</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="D3" s="10" t="s">
         <v>112</v>
       </c>
@@ -1474,7 +1489,7 @@
       </c>
       <c r="L3" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>69</v>
@@ -1511,11 +1526,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>45786</v>
+        <v>45796</v>
       </c>
       <c r="Y3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45837</v>
+        <v>45847</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>83</v>
@@ -1579,11 +1594,11 @@
       </c>
       <c r="AT3" s="18">
         <f t="shared" ca="1" si="3"/>
-        <v>45785</v>
+        <v>45795</v>
       </c>
       <c r="AU3" s="18">
         <f t="shared" ca="1" si="4"/>
-        <v>45785</v>
+        <v>45795</v>
       </c>
       <c r="AV3" s="29" t="str">
         <f t="shared" si="5"/>
@@ -1601,9 +1616,9 @@
       <c r="AZ3" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="BA3" s="31" t="str">
+      <c r="BA3" s="32" t="str">
         <f ca="1">AZ10</f>
-        <v>BA35334CJ</v>
+        <v>BA59596CJ</v>
       </c>
       <c r="BB3" s="11" t="s">
         <v>69</v>
@@ -1611,14 +1626,14 @@
       <c r="BC3" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="BD3" s="32" t="str">
+      <c r="BD3" s="33" t="str">
         <f ca="1">BH10</f>
-        <v>MTKNBN20D20A694A</v>
+        <v>MTKNBN20D20A714A</v>
       </c>
       <c r="BE3" t="s">
         <v>101</v>
       </c>
-      <c r="BF3" s="33">
+      <c r="BF3" s="34">
         <v>35591</v>
       </c>
       <c r="BG3" s="11" t="s">
@@ -1633,7 +1648,7 @@
       <c r="BJ3" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BK3" s="33" t="s">
+      <c r="BK3" s="34" t="s">
         <v>104</v>
       </c>
       <c r="BL3" s="11" t="s">
@@ -1658,10 +1673,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.35">
       <c r="C4" s="9"/>
       <c r="AZ4" s="7"/>
-      <c r="BA4" s="34"/>
+      <c r="BA4" s="35"/>
     </row>
     <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="C5" s="9"/>
@@ -1682,28 +1697,28 @@
       </c>
       <c r="AX9">
         <f t="array" aca="1" ref="AX9:AX23" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>76001</v>
+        <v>73464</v>
       </c>
       <c r="AY9" t="s">
         <v>122</v>
       </c>
       <c r="AZ9" t="str">
         <f ca="1">AW9&amp;AX9&amp;AY9</f>
-        <v>AB76001JC</v>
-      </c>
-      <c r="BD9" s="32" t="s">
+        <v>AB73464JC</v>
+      </c>
+      <c r="BD9" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE9">
         <f t="array" aca="1" ref="BE9:BE23" ca="1">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>322</v>
+        <v>236</v>
       </c>
       <c r="BG9" t="s">
         <v>124</v>
       </c>
       <c r="BH9" t="str">
         <f ca="1">BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A322A</v>
+        <v>MTKBNN10D10A236A</v>
       </c>
     </row>
     <row r="10" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1713,28 +1728,28 @@
       </c>
       <c r="AX10">
         <f ca="1"/>
-        <v>35334</v>
+        <v>59596</v>
       </c>
       <c r="AY10" t="s">
         <v>126</v>
       </c>
       <c r="AZ10" t="str">
         <f t="shared" ref="AZ10:AZ23" ca="1" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA35334CJ</v>
-      </c>
-      <c r="BD10" s="32" t="s">
+        <v>BA59596CJ</v>
+      </c>
+      <c r="BD10" s="33" t="s">
         <v>127</v>
       </c>
       <c r="BE10">
         <f ca="1"/>
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="BG10" t="s">
         <v>124</v>
       </c>
       <c r="BH10" t="str">
         <f t="shared" ref="BH10:BH23" ca="1" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A694A</v>
+        <v>MTKNBN20D20A714A</v>
       </c>
     </row>
     <row r="11" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1744,28 +1759,28 @@
       </c>
       <c r="AX11">
         <f ca="1"/>
-        <v>75717</v>
+        <v>39139</v>
       </c>
       <c r="AY11" t="s">
         <v>122</v>
       </c>
       <c r="AZ11" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB75717JC</v>
-      </c>
-      <c r="BD11" s="32" t="s">
+        <v>AB39139JC</v>
+      </c>
+      <c r="BD11" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE11">
         <f ca="1"/>
-        <v>962</v>
+        <v>338</v>
       </c>
       <c r="BG11" t="s">
         <v>124</v>
       </c>
       <c r="BH11" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A962A</v>
+        <v>MTKBNN10D10A338A</v>
       </c>
     </row>
     <row r="12" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1775,28 +1790,28 @@
       </c>
       <c r="AX12">
         <f ca="1"/>
-        <v>35938</v>
+        <v>58206</v>
       </c>
       <c r="AY12" t="s">
         <v>126</v>
       </c>
       <c r="AZ12" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA35938CJ</v>
-      </c>
-      <c r="BD12" s="32" t="s">
+        <v>BA58206CJ</v>
+      </c>
+      <c r="BD12" s="33" t="s">
         <v>127</v>
       </c>
       <c r="BE12">
         <f ca="1"/>
-        <v>949</v>
+        <v>283</v>
       </c>
       <c r="BG12" t="s">
         <v>124</v>
       </c>
       <c r="BH12" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A949A</v>
+        <v>MTKNBN20D20A283A</v>
       </c>
     </row>
     <row r="13" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1806,28 +1821,28 @@
       </c>
       <c r="AX13">
         <f ca="1"/>
-        <v>16553</v>
+        <v>78907</v>
       </c>
       <c r="AY13" t="s">
         <v>122</v>
       </c>
       <c r="AZ13" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB16553JC</v>
-      </c>
-      <c r="BD13" s="32" t="s">
+        <v>AB78907JC</v>
+      </c>
+      <c r="BD13" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE13">
         <f ca="1"/>
-        <v>476</v>
+        <v>511</v>
       </c>
       <c r="BG13" t="s">
         <v>124</v>
       </c>
       <c r="BH13" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A476A</v>
+        <v>MTKBNN10D10A511A</v>
       </c>
     </row>
     <row r="14" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1837,28 +1852,28 @@
       </c>
       <c r="AX14">
         <f ca="1"/>
-        <v>48038</v>
+        <v>75301</v>
       </c>
       <c r="AY14" t="s">
         <v>126</v>
       </c>
       <c r="AZ14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA48038CJ</v>
-      </c>
-      <c r="BD14" s="32" t="s">
+        <v>BA75301CJ</v>
+      </c>
+      <c r="BD14" s="33" t="s">
         <v>127</v>
       </c>
       <c r="BE14">
         <f ca="1"/>
-        <v>382</v>
+        <v>193</v>
       </c>
       <c r="BG14" t="s">
         <v>124</v>
       </c>
       <c r="BH14" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A382A</v>
+        <v>MTKNBN20D20A193A</v>
       </c>
     </row>
     <row r="15" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1868,28 +1883,28 @@
       </c>
       <c r="AX15">
         <f ca="1"/>
-        <v>93019</v>
+        <v>26947</v>
       </c>
       <c r="AY15" t="s">
         <v>122</v>
       </c>
       <c r="AZ15" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB93019JC</v>
-      </c>
-      <c r="BD15" s="32" t="s">
+        <v>AB26947JC</v>
+      </c>
+      <c r="BD15" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE15">
         <f ca="1"/>
-        <v>907</v>
+        <v>790</v>
       </c>
       <c r="BG15" t="s">
         <v>124</v>
       </c>
       <c r="BH15" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A907A</v>
+        <v>MTKBNN10D10A790A</v>
       </c>
     </row>
     <row r="16" spans="1:70" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1899,28 +1914,28 @@
       </c>
       <c r="AX16">
         <f ca="1"/>
-        <v>12745</v>
+        <v>17457</v>
       </c>
       <c r="AY16" t="s">
         <v>126</v>
       </c>
       <c r="AZ16" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA12745CJ</v>
-      </c>
-      <c r="BD16" s="32" t="s">
+        <v>BA17457CJ</v>
+      </c>
+      <c r="BD16" s="33" t="s">
         <v>127</v>
       </c>
       <c r="BE16">
         <f ca="1"/>
-        <v>784</v>
+        <v>170</v>
       </c>
       <c r="BG16" t="s">
         <v>124</v>
       </c>
       <c r="BH16" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A784A</v>
+        <v>MTKNBN20D20A170A</v>
       </c>
     </row>
     <row r="17" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1930,28 +1945,28 @@
       </c>
       <c r="AX17">
         <f ca="1"/>
-        <v>47691</v>
+        <v>12612</v>
       </c>
       <c r="AY17" t="s">
         <v>122</v>
       </c>
       <c r="AZ17" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB47691JC</v>
-      </c>
-      <c r="BD17" s="32" t="s">
+        <v>AB12612JC</v>
+      </c>
+      <c r="BD17" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE17">
         <f ca="1"/>
-        <v>487</v>
+        <v>844</v>
       </c>
       <c r="BG17" t="s">
         <v>124</v>
       </c>
       <c r="BH17" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A487A</v>
+        <v>MTKBNN10D10A844A</v>
       </c>
     </row>
     <row r="18" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1961,28 +1976,28 @@
       </c>
       <c r="AX18">
         <f ca="1"/>
-        <v>70762</v>
+        <v>99061</v>
       </c>
       <c r="AY18" t="s">
         <v>126</v>
       </c>
       <c r="AZ18" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA70762CJ</v>
-      </c>
-      <c r="BD18" s="32" t="s">
+        <v>BA99061CJ</v>
+      </c>
+      <c r="BD18" s="33" t="s">
         <v>127</v>
       </c>
       <c r="BE18">
         <f ca="1"/>
-        <v>890</v>
+        <v>568</v>
       </c>
       <c r="BG18" t="s">
         <v>124</v>
       </c>
       <c r="BH18" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A890A</v>
+        <v>MTKNBN20D20A568A</v>
       </c>
     </row>
     <row r="19" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1991,28 +2006,28 @@
       </c>
       <c r="AX19">
         <f ca="1"/>
-        <v>63720</v>
+        <v>35921</v>
       </c>
       <c r="AY19" t="s">
         <v>122</v>
       </c>
       <c r="AZ19" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB63720JC</v>
-      </c>
-      <c r="BD19" s="32" t="s">
+        <v>AB35921JC</v>
+      </c>
+      <c r="BD19" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE19">
         <f ca="1"/>
-        <v>129</v>
+        <v>828</v>
       </c>
       <c r="BG19" t="s">
         <v>124</v>
       </c>
       <c r="BH19" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A129A</v>
+        <v>MTKBNN10D10A828A</v>
       </c>
     </row>
     <row r="20" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2021,28 +2036,28 @@
       </c>
       <c r="AX20">
         <f ca="1"/>
-        <v>43549</v>
+        <v>16806</v>
       </c>
       <c r="AY20" t="s">
         <v>126</v>
       </c>
       <c r="AZ20" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA43549CJ</v>
-      </c>
-      <c r="BD20" s="32" t="s">
+        <v>BA16806CJ</v>
+      </c>
+      <c r="BD20" s="33" t="s">
         <v>127</v>
       </c>
       <c r="BE20">
         <f ca="1"/>
-        <v>676</v>
+        <v>503</v>
       </c>
       <c r="BG20" t="s">
         <v>124</v>
       </c>
       <c r="BH20" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A676A</v>
+        <v>MTKNBN20D20A503A</v>
       </c>
     </row>
     <row r="21" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2051,28 +2066,28 @@
       </c>
       <c r="AX21">
         <f ca="1"/>
-        <v>18605</v>
+        <v>97825</v>
       </c>
       <c r="AY21" t="s">
         <v>122</v>
       </c>
       <c r="AZ21" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB18605JC</v>
-      </c>
-      <c r="BD21" s="32" t="s">
+        <v>AB97825JC</v>
+      </c>
+      <c r="BD21" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE21">
         <f ca="1"/>
-        <v>201</v>
+        <v>605</v>
       </c>
       <c r="BG21" t="s">
         <v>124</v>
       </c>
       <c r="BH21" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A201A</v>
+        <v>MTKBNN10D10A605A</v>
       </c>
     </row>
     <row r="22" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2081,28 +2096,28 @@
       </c>
       <c r="AX22">
         <f ca="1"/>
-        <v>65277</v>
+        <v>73036</v>
       </c>
       <c r="AY22" t="s">
         <v>126</v>
       </c>
       <c r="AZ22" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BA65277CJ</v>
-      </c>
-      <c r="BD22" s="32" t="s">
+        <v>BA73036CJ</v>
+      </c>
+      <c r="BD22" s="33" t="s">
         <v>127</v>
       </c>
       <c r="BE22">
         <f ca="1"/>
-        <v>730</v>
+        <v>515</v>
       </c>
       <c r="BG22" t="s">
         <v>124</v>
       </c>
       <c r="BH22" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKNBN20D20A730A</v>
+        <v>MTKNBN20D20A515A</v>
       </c>
     </row>
     <row r="23" spans="3:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2111,28 +2126,28 @@
       </c>
       <c r="AX23">
         <f ca="1"/>
-        <v>60009</v>
+        <v>46268</v>
       </c>
       <c r="AY23" t="s">
         <v>122</v>
       </c>
       <c r="AZ23" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AB60009JC</v>
-      </c>
-      <c r="BD23" s="32" t="s">
+        <v>AB46268JC</v>
+      </c>
+      <c r="BD23" s="33" t="s">
         <v>123</v>
       </c>
       <c r="BE23">
         <f ca="1"/>
-        <v>850</v>
+        <v>654</v>
       </c>
       <c r="BG23" t="s">
         <v>124</v>
       </c>
       <c r="BH23" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>MTKBNN10D10A850A</v>
+        <v>MTKBNN10D10A654A</v>
       </c>
     </row>
   </sheetData>
@@ -2149,6 +2164,6 @@
     <hyperlink ref="U3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId6"/>
 </worksheet>
 </file>